--- a/개발 목록.xlsx
+++ b/개발 목록.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Moon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A273CE-2BE4-40A0-8FE1-FDFAB239F8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8667FC25-D307-4EB3-9295-D0CD1B68ADEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="4110" windowWidth="22680" windowHeight="11370" xr2:uid="{6BEBE30E-AE67-4A73-A5DF-F2D22843DDA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6BEBE30E-AE67-4A73-A5DF-F2D22843DDA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="완료목록" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="난이도">Sheet1!$J$3:$J$5</definedName>
-    <definedName name="등급">Sheet1!$J$3:$J$5</definedName>
-    <definedName name="카테고리">Sheet1!$I$3:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$L$19</definedName>
+    <definedName name="난이도">Sheet1!$K$3:$K$5</definedName>
+    <definedName name="등급">Sheet1!$K$3:$K$5</definedName>
+    <definedName name="카테고리">Sheet1!$J$3:$J$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="81">
   <si>
     <t>기능</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -291,6 +292,88 @@
   </si>
   <si>
     <t>PrimitiveDatasPerType을 매 프레임마다 갱신해 줌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포인트 라이트 최적화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ctrl+C, Crtl+V 로 액터 복사 붙여넣기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 위치, Cascade Frustum의 Near Far에 활용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이캐스팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambient 시리얼라이즈 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSAO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리버스 뎁스 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼 곳에 정밀도를 더 부여해서 그림자 여드름 방지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미시브</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박스, 가우시안 블러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감마 보정 고려</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종 렌더 타겟 뷰 포맷 모디파이어를 SRGB로 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal Offset Bias 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림자 여드름 방지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규기능</t>
+  </si>
+  <si>
+    <t>신규기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개선</t>
+  </si>
+  <si>
+    <t>개선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Renderer 쪽에 있는 변수를 DirectionalLightComp로 옮김</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -329,7 +412,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,18 +422,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,7 +467,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -406,22 +477,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -758,18 +823,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16947ED2-D3B6-499F-ABD6-068CEB91F43A}">
-  <dimension ref="B2:J22"/>
+  <dimension ref="B2:L22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="40.125" customWidth="1"/>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="22.625" customWidth="1"/>
-    <col min="6" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="59.125" customWidth="1"/>
-    <col min="8" max="8" width="51.875" customWidth="1"/>
+    <col min="4" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="22.625" customWidth="1"/>
+    <col min="7" max="7" width="19.125" customWidth="1"/>
+    <col min="8" max="8" width="59.125" customWidth="1"/>
+    <col min="9" max="9" width="51.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:12">
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,25 +842,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="L2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
@@ -803,21 +874,27 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="H3" s="2"/>
-      <c r="I3" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" t="s">
         <v>3</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="2:10">
+      <c r="L3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
@@ -825,21 +902,27 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="H4" s="2"/>
-      <c r="I4" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="2:10">
+      <c r="L4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
@@ -847,21 +930,27 @@
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="H5" s="2"/>
-      <c r="I5" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" t="s">
         <v>12</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="2:10">
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
@@ -869,17 +958,20 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="2:10">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="2:12">
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
@@ -887,31 +979,37 @@
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="C8" s="7" t="s">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="2:10" ht="33">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="2:12" ht="33">
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
@@ -919,20 +1017,20 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="5">
-        <v>3</v>
-      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="2:12">
       <c r="C10" s="2" t="s">
         <v>24</v>
       </c>
@@ -940,34 +1038,37 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="3">
-        <v>2</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="C11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="2:10">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="2:12">
       <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
@@ -975,15 +1076,18 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="2:10">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="2:12">
       <c r="C13" s="2" t="s">
         <v>35</v>
       </c>
@@ -991,15 +1095,21 @@
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="2:10">
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
@@ -1007,88 +1117,132 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="3:8">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="C16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="3:8">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="2:9">
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="3:8">
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="2:9">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="3:8">
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="2:9">
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="3:8">
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="2:9">
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="3:8">
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="2:9">
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D20" xr:uid="{4BD7259B-FEAA-42EC-B6AF-05B73FFDD1AC}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D21" xr:uid="{4BD7259B-FEAA-42EC-B6AF-05B73FFDD1AC}">
       <formula1>카테고리</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F24" xr:uid="{1178DF92-493E-4161-9394-4412D107EB84}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G24" xr:uid="{1178DF92-493E-4161-9394-4412D107EB84}">
       <formula1>등급</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E16 E18:E25" xr:uid="{EB33ED47-7B9B-466E-9BC2-DD8665F5A77F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F25 F3:F15" xr:uid="{EB33ED47-7B9B-466E-9BC2-DD8665F5A77F}">
       <formula1>난이도</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E22" xr:uid="{40E67A10-B5A9-49AC-A511-F0CA36D3B042}">
+      <formula1>$L$3:$L$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1097,15 +1251,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4EE942-23CD-423A-93F0-F960FE01E86A}">
-  <dimension ref="B1:G40"/>
+  <dimension ref="B1:H40"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="40.125" customWidth="1"/>
-    <col min="6" max="6" width="48.375" customWidth="1"/>
-    <col min="7" max="7" width="80.875" customWidth="1"/>
+    <col min="7" max="7" width="48.375" customWidth="1"/>
+    <col min="8" max="8" width="80.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:8">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,471 +1267,578 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:8">
       <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="2:7">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="2:7" ht="49.5">
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="2:8" ht="49.5">
       <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="49.5">
+    <row r="5" spans="2:8" ht="49.5">
       <c r="B5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="99">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="2:8" ht="99">
+      <c r="B6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:8">
       <c r="B7" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="2:7">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="2:8">
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="2:7">
+      <c r="G8" s="4"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="2:8">
       <c r="B9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="33">
+    <row r="10" spans="2:8" ht="33">
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="33">
+    <row r="11" spans="2:8" ht="33">
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="49.5">
+    <row r="12" spans="2:8" ht="49.5">
       <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="99">
+    <row r="13" spans="2:8" ht="99">
       <c r="B13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:8">
       <c r="B14" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+    <row r="15" spans="2:8">
+      <c r="B15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="H19" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="2:8">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="2:8">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="2:8">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="2:8">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="2:7">
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="2:8">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="2:7">
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="2:8">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="2:7">
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="2:8">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="2:7">
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="2:8">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="2:7">
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="2:7">
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="2:8">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="2:7">
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="2:8">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="2:7">
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="2:8">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="2:7">
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="2:8">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="2:7">
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="2:8">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="2:7">
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="2:8">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="2:7">
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="2:8">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="2:7">
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="2:8">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="2:8">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="2:7">
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="2:8">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="2:8">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E14" xr:uid="{E5520149-5341-4E12-AB2E-7036A578FC33}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F34" xr:uid="{E5520149-5341-4E12-AB2E-7036A578FC33}">
       <formula1>등급</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D14" xr:uid="{DB41F2AC-CCD9-48B5-8FDE-B4F5EC5C5F56}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E34" xr:uid="{DB41F2AC-CCD9-48B5-8FDE-B4F5EC5C5F56}">
       <formula1>난이도</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C14" xr:uid="{0158A335-96F6-4473-B97F-347A3C2CEAC1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C34 D21:D34" xr:uid="{0158A335-96F6-4473-B97F-347A3C2CEAC1}">
       <formula1>카테고리</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20" xr:uid="{425D89FE-68D5-4173-9022-B0822408A974}">
+      <formula1>$L$3:$L$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/개발 목록.xlsx
+++ b/개발 목록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Moon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8667FC25-D307-4EB3-9295-D0CD1B68ADEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB13C3A-7604-426E-9E9E-105E07541BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6BEBE30E-AE67-4A73-A5DF-F2D22843DDA1}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
   <si>
     <t>기능</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,6 +374,11 @@
   </si>
   <si>
     <t>Renderer 쪽에 있는 변수를 DirectionalLightComp로 옮김</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GS로 추가 삼각형을 만들어 각 면에 렌더링하는 것을 제거.
+인스턴싱을 활용하고, GS는 RTArrayIndex를 전달하기 위한 패스쓰루로 활용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1108,7 +1113,7 @@
     </row>
     <row r="14" spans="2:12">
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>36</v>
@@ -1130,61 +1135,51 @@
     </row>
     <row r="15" spans="2:12">
       <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="2:12">
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="2:9">
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>76</v>
-      </c>
+    <row r="17" spans="3:9">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="3:9">
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1193,7 +1188,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="3:9">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -1202,7 +1197,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="3:9">
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1211,7 +1206,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="3:9">
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1220,7 +1215,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="3:9">
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1238,7 +1233,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G24" xr:uid="{1178DF92-493E-4161-9394-4412D107EB84}">
       <formula1>등급</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F25 F3:F15" xr:uid="{EB33ED47-7B9B-466E-9BC2-DD8665F5A77F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16:F25 F3:F14" xr:uid="{EB33ED47-7B9B-466E-9BC2-DD8665F5A77F}">
       <formula1>난이도</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E22" xr:uid="{40E67A10-B5A9-49AC-A511-F0CA36D3B042}">
@@ -1645,14 +1640,26 @@
       <c r="G20" s="4"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+    <row r="21" spans="2:8" ht="33">
+      <c r="B21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="2"/>
@@ -1834,10 +1841,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E34" xr:uid="{DB41F2AC-CCD9-48B5-8FDE-B4F5EC5C5F56}">
       <formula1>난이도</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C34 D21:D34" xr:uid="{0158A335-96F6-4473-B97F-347A3C2CEAC1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22:D34 C2:C34" xr:uid="{0158A335-96F6-4473-B97F-347A3C2CEAC1}">
       <formula1>카테고리</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20" xr:uid="{425D89FE-68D5-4173-9022-B0822408A974}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D21" xr:uid="{425D89FE-68D5-4173-9022-B0822408A974}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
   </dataValidations>
